--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.08230524905302</v>
+        <v>5.050874602971116</v>
       </c>
       <c r="D2" t="n">
-        <v>31.28894379519476</v>
+        <v>5.084453366719148</v>
       </c>
       <c r="E2" t="n">
-        <v>8.53656987657644</v>
+        <v>1.387192604943672</v>
       </c>
       <c r="F2" t="n">
-        <v>2.366234751653925</v>
+        <v>0.3845131471437629</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.7239413866885</v>
+        <v>8.242640475336882</v>
       </c>
       <c r="D3" t="n">
-        <v>34.11173857916575</v>
+        <v>5.543157519114434</v>
       </c>
       <c r="E3" t="n">
-        <v>8.53656987657644</v>
+        <v>1.387192604943672</v>
       </c>
       <c r="F3" t="n">
-        <v>2.366234751653925</v>
+        <v>0.3845131471437629</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.225208179262</v>
+        <v>6.374096329130076</v>
       </c>
       <c r="D4" t="n">
-        <v>29.49414935527733</v>
+        <v>4.792799270232567</v>
       </c>
       <c r="E4" t="n">
-        <v>8.53656987657644</v>
+        <v>1.387192604943672</v>
       </c>
       <c r="F4" t="n">
-        <v>2.366234751653925</v>
+        <v>0.3845131471437629</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.69977019952235</v>
+        <v>8.401212657422382</v>
       </c>
       <c r="D5" t="n">
-        <v>27.70578638369314</v>
+        <v>4.502190287350135</v>
       </c>
       <c r="E5" t="n">
-        <v>8.53656987657644</v>
+        <v>1.387192604943672</v>
       </c>
       <c r="F5" t="n">
-        <v>2.366234751653925</v>
+        <v>0.3845131471437629</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
